--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -505,6 +505,9 @@
         <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
 white_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F9" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -563,7 +566,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015101015124100</v>
+        <v>0151010151241020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -509,9 +509,92 @@
         <v>20</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>3</v>
+      </c>
+      <c r="C10" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F10" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F11" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F13" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F14" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F15" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>276_情迷罗拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>449_柔丽思 绿_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -566,7 +649,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151010151241020</v>
+        <v>0151010151241020813101515155760</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -591,6 +591,9 @@
       <c r="C19" t="str">
         <v>449_柔丽思 绿_undefined_undefined_1bunch</v>
       </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -649,7 +652,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151010151241020813101515155760</v>
+        <v>01510101512410208131015151557610</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -595,9 +595,90 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
+（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -652,7 +733,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01510101512410208131015151557610</v>
+        <v>01510101512410208131015151557610551555101510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -675,6 +675,9 @@
       <c r="C29" t="str">
         <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
       </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -733,7 +736,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01510101512410208131015151557610551555101510100</v>
+        <v>01510101512410208131015151557610551555101510105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -679,9 +679,91 @@
         <v>5</v>
       </c>
     </row>
+    <row r="30" xml:space="preserve">
+      <c r="C30" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">740_袋鼠爪橙_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>45_拉丝艳粉_Spider pink+_Gerbera L._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>6</v>
+      </c>
+      <c r="C36" t="str">
+        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>780_贝壳草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L39"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -736,7 +818,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01510101512410208131015151557610551555101510105</v>
+        <v>015101015124102081310151515576105515551015101055510152010205200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -760,6 +760,9 @@
       <c r="A39" t="str">
         <v>7</v>
       </c>
+      <c r="C39" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -763,6 +763,9 @@
       <c r="C39" t="str">
         <v>646_芍药莎拉_Sarah_undefined_5stems</v>
       </c>
+      <c r="F39" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -821,7 +824,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015101015124102081310151515576105515551015101055510152010205200</v>
+        <v>015101015124102081310151515576105515551015101055510152010205203</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -764,7 +764,7 @@
         <v>646_芍药莎拉_Sarah_undefined_5stems</v>
       </c>
       <c r="F39" t="str">
-        <v>3</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +824,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015101015124102081310151515576105515551015101055510152010205203</v>
+        <v>01510101512410208131015151557610551555101510105551015201020520300</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -767,9 +767,37 @@
         <v>300</v>
       </c>
     </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>8</v>
+      </c>
+      <c r="C40" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L42"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -824,7 +852,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01510101512410208131015151557610551555101510105551015201020520300</v>
+        <v>0151010151241020813101515155761055155510151010555101520102052030020510</v>
       </c>
     </row>
   </sheetData>
